--- a/Comparaison_programmes.xlsx
+++ b/Comparaison_programmes.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
   <si>
     <t>Colonnes : Thème, Problématique, Priorité
 Lignes : Candidat, Parti Politique</t>
@@ -140,24 +140,60 @@
     <t>Vieillesse et Fin de Vie</t>
   </si>
   <si>
+    <t>POPO</t>
+  </si>
+  <si>
+    <t>SUUUUUUUUU</t>
+  </si>
+  <si>
+    <t>UU</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>DE</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
     <t>Nathalie Arthaud</t>
   </si>
   <si>
     <t>Lutte Ouvrière (LO)</t>
   </si>
   <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>François Asselineau</t>
   </si>
   <si>
     <t>Union Populaire Républicaine (UPR)</t>
   </si>
   <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>Gabriel Attal</t>
   </si>
   <si>
     <t>Renaissance (RE)</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Delphine Batho</t>
   </si>
   <si>
@@ -170,6 +206,9 @@
     <t>Les Républicains (LR)</t>
   </si>
   <si>
+    <t>D</t>
+  </si>
+  <si>
     <t>Karim Bouamrane</t>
   </si>
   <si>
@@ -185,6 +224,9 @@
     <t>Jérôme Guedj</t>
   </si>
   <si>
+    <t>c</t>
+  </si>
+  <si>
     <t>Anasse Kazib</t>
   </si>
   <si>
@@ -197,6 +239,9 @@
     <t>Nouveau Parti Anticapitaliste Révolutionnaire (NPA)</t>
   </si>
   <si>
+    <t>d</t>
+  </si>
+  <si>
     <t>Marine Le Pen</t>
   </si>
   <si>
@@ -207,6 +252,9 @@
   </si>
   <si>
     <t>La France Insoumise (LFI)</t>
+  </si>
+  <si>
+    <t>V</t>
   </si>
   <si>
     <t>Édouard Philippe</t>
@@ -1147,12 +1195,24 @@
     <row r="2" ht="36.75" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="11"/>
+      <c r="C2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>47</v>
+      </c>
       <c r="I2" s="12"/>
       <c r="J2" s="8"/>
       <c r="K2" s="10"/>
@@ -1234,15 +1294,9 @@
     <row r="3" ht="36.75" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15"/>
-      <c r="C3" s="16">
-        <v>5.0</v>
-      </c>
-      <c r="D3" s="17">
-        <v>5.0</v>
-      </c>
-      <c r="E3" s="18">
-        <v>5.0</v>
-      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="18"/>
       <c r="F3" s="19"/>
       <c r="G3" s="20"/>
       <c r="H3" s="19"/>
@@ -1326,14 +1380,20 @@
     </row>
     <row r="4" ht="36.75" customHeight="1">
       <c r="A4" s="22" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="26"/>
+        <v>49</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>50</v>
+      </c>
       <c r="F4" s="27"/>
       <c r="G4" s="28"/>
       <c r="H4" s="27"/>
@@ -1417,17 +1477,29 @@
     </row>
     <row r="5" ht="36.75" customHeight="1">
       <c r="A5" s="22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="11"/>
+        <v>52</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>55</v>
+      </c>
       <c r="I5" s="12"/>
       <c r="J5" s="8"/>
       <c r="K5" s="10"/>
@@ -1508,17 +1580,23 @@
     </row>
     <row r="6" ht="36.75" customHeight="1">
       <c r="A6" s="31" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C6" s="31"/>
-      <c r="D6" s="9"/>
+      <c r="D6" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
+      <c r="F6" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="G6" s="12"/>
-      <c r="H6" s="11"/>
+      <c r="H6" s="11" t="s">
+        <v>59</v>
+      </c>
       <c r="I6" s="12"/>
       <c r="J6" s="8"/>
       <c r="K6" s="10"/>
@@ -1599,15 +1677,19 @@
     </row>
     <row r="7" ht="36.75" customHeight="1">
       <c r="A7" s="31" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="C7" s="31"/>
-      <c r="D7" s="9"/>
+      <c r="D7" s="9" t="s">
+        <v>50</v>
+      </c>
       <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="F7" s="11" t="s">
+        <v>53</v>
+      </c>
       <c r="G7" s="12"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -1690,16 +1772,22 @@
     </row>
     <row r="8" ht="36.75" customHeight="1">
       <c r="A8" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="31"/>
+      <c r="D8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="9"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="11"/>
-      <c r="G8" s="12"/>
+      <c r="F8" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
       <c r="J8" s="8"/>
@@ -1781,16 +1869,24 @@
     </row>
     <row r="9" ht="36.75" customHeight="1">
       <c r="A9" s="31" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="31"/>
+      <c r="D9" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="12"/>
+      <c r="F9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
       <c r="J9" s="8"/>
@@ -1872,16 +1968,24 @@
     </row>
     <row r="10" ht="36.75" customHeight="1">
       <c r="A10" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="31"/>
+      <c r="D10" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="12"/>
+      <c r="G10" s="12" t="s">
+        <v>53</v>
+      </c>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
       <c r="J10" s="8"/>
@@ -1963,15 +2067,21 @@
     </row>
     <row r="11" ht="36.75" customHeight="1">
       <c r="A11" s="31" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C11" s="31"/>
+      <c r="D11" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="11"/>
+      <c r="F11" s="11" t="s">
+        <v>54</v>
+      </c>
       <c r="G11" s="12"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -2054,16 +2164,22 @@
     </row>
     <row r="12" ht="36.75" customHeight="1">
       <c r="A12" s="31" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="C12" s="31"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="10"/>
+      <c r="D12" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="F12" s="11"/>
-      <c r="G12" s="12"/>
+      <c r="G12" s="12" t="s">
+        <v>54</v>
+      </c>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
       <c r="J12" s="8"/>
@@ -2145,13 +2261,17 @@
     </row>
     <row r="13" ht="36.75" customHeight="1">
       <c r="A13" s="31" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="9"/>
+        <v>74</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>75</v>
+      </c>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
       <c r="G13" s="12"/>
@@ -2236,13 +2356,17 @@
     </row>
     <row r="14" ht="36.75" customHeight="1">
       <c r="A14" s="31" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="9"/>
+        <v>77</v>
+      </c>
+      <c r="C14" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>53</v>
+      </c>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
       <c r="G14" s="12"/>
@@ -2327,13 +2451,17 @@
     </row>
     <row r="15" ht="36.75" customHeight="1">
       <c r="A15" s="31" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C15" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="9"/>
+      <c r="D15" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="E15" s="10"/>
       <c r="F15" s="11"/>
       <c r="G15" s="12"/>
@@ -2418,13 +2546,15 @@
     </row>
     <row r="16" ht="36.75" customHeight="1">
       <c r="A16" s="31" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C16" s="31"/>
-      <c r="D16" s="9"/>
+      <c r="D16" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="E16" s="10"/>
       <c r="F16" s="11"/>
       <c r="G16" s="12"/>
@@ -2509,13 +2639,15 @@
     </row>
     <row r="17" ht="36.75" customHeight="1">
       <c r="A17" s="32" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C17" s="31"/>
-      <c r="D17" s="9"/>
+      <c r="D17" s="9" t="s">
+        <v>80</v>
+      </c>
       <c r="E17" s="10"/>
       <c r="F17" s="11"/>
       <c r="G17" s="12"/>
@@ -2600,10 +2732,10 @@
     </row>
     <row r="18" ht="36.75" customHeight="1">
       <c r="A18" s="33" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C18" s="35"/>
       <c r="D18" s="36"/>

--- a/Comparaison_programmes.xlsx
+++ b/Comparaison_programmes.xlsx
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="86">
   <si>
-    <t>Colonnes : Thème, Problématique, Priorité
+    <t>Colonnes : Thème, Problématique
 Lignes : Candidat, Parti Politique</t>
   </si>
   <si>
@@ -312,7 +312,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="39">
+  <borders count="32">
     <border/>
     <border>
       <left style="medium">
@@ -353,11 +353,17 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <right style="thin">
@@ -432,28 +438,88 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
-      <bottom style="medium">
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
     </border>
     <border>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-    </border>
-    <border>
-      <left style="thin">
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
@@ -468,122 +534,6 @@
         <color rgb="FF000000"/>
       </left>
       <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
@@ -691,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="34">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -724,8 +674,12 @@
     <xf borderId="12" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="14" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -738,6 +692,9 @@
     <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="19" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -762,9 +719,6 @@
     <xf borderId="26" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="27" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -778,27 +732,6 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="31" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="32" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="33" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="34" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="35" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="36" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="37" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="38" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1292,18 +1225,28 @@
       <c r="CG2" s="10"/>
     </row>
     <row r="3" ht="36.75" customHeight="1">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18"/>
+      <c r="A3" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>50</v>
+      </c>
       <c r="F3" s="19"/>
       <c r="G3" s="20"/>
       <c r="H3" s="19"/>
       <c r="I3" s="20"/>
-      <c r="J3" s="16"/>
+      <c r="J3" s="21"/>
       <c r="K3" s="18"/>
-      <c r="L3" s="21"/>
+      <c r="L3" s="22"/>
       <c r="M3" s="18"/>
       <c r="N3" s="19"/>
       <c r="O3" s="18"/>
@@ -1337,7 +1280,7 @@
       <c r="AQ3" s="18"/>
       <c r="AR3" s="19"/>
       <c r="AS3" s="18"/>
-      <c r="AT3" s="16"/>
+      <c r="AT3" s="21"/>
       <c r="AU3" s="18"/>
       <c r="AV3" s="19"/>
       <c r="AW3" s="18"/>
@@ -1379,126 +1322,126 @@
       <c r="CG3" s="18"/>
     </row>
     <row r="4" ht="36.75" customHeight="1">
-      <c r="A4" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="24" t="s">
+      <c r="A4" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="26"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="26"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="26"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="26"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="26"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="26"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="26"/>
-      <c r="Z4" s="27"/>
-      <c r="AA4" s="26"/>
-      <c r="AB4" s="27"/>
-      <c r="AC4" s="26"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="26"/>
-      <c r="AF4" s="27"/>
-      <c r="AG4" s="26"/>
-      <c r="AH4" s="27"/>
-      <c r="AI4" s="26"/>
-      <c r="AJ4" s="27"/>
-      <c r="AK4" s="26"/>
-      <c r="AL4" s="27"/>
-      <c r="AM4" s="26"/>
-      <c r="AN4" s="27"/>
-      <c r="AO4" s="26"/>
-      <c r="AP4" s="27"/>
-      <c r="AQ4" s="26"/>
-      <c r="AR4" s="27"/>
-      <c r="AS4" s="26"/>
-      <c r="AT4" s="29"/>
-      <c r="AU4" s="26"/>
-      <c r="AV4" s="27"/>
-      <c r="AW4" s="26"/>
-      <c r="AX4" s="27"/>
-      <c r="AY4" s="26"/>
-      <c r="AZ4" s="27"/>
-      <c r="BA4" s="26"/>
-      <c r="BB4" s="27"/>
-      <c r="BC4" s="26"/>
-      <c r="BD4" s="27"/>
-      <c r="BE4" s="26"/>
-      <c r="BF4" s="27"/>
-      <c r="BG4" s="26"/>
-      <c r="BH4" s="27"/>
-      <c r="BI4" s="26"/>
-      <c r="BJ4" s="27"/>
-      <c r="BK4" s="26"/>
-      <c r="BL4" s="27"/>
-      <c r="BM4" s="26"/>
-      <c r="BN4" s="27"/>
-      <c r="BO4" s="26"/>
-      <c r="BP4" s="27"/>
-      <c r="BQ4" s="26"/>
-      <c r="BR4" s="27"/>
-      <c r="BS4" s="26"/>
-      <c r="BT4" s="27"/>
-      <c r="BU4" s="26"/>
-      <c r="BV4" s="27"/>
-      <c r="BW4" s="26"/>
-      <c r="BX4" s="27"/>
-      <c r="BY4" s="26"/>
-      <c r="BZ4" s="27"/>
-      <c r="CA4" s="26"/>
-      <c r="CB4" s="27"/>
-      <c r="CC4" s="26"/>
-      <c r="CD4" s="27"/>
-      <c r="CE4" s="26"/>
-      <c r="CF4" s="27"/>
-      <c r="CG4" s="26"/>
+      <c r="F4" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I4" s="12"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="11"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="11"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="11"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="11"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="11"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="11"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="11"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="11"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="11"/>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="11"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="11"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="11"/>
+      <c r="AM4" s="10"/>
+      <c r="AN4" s="11"/>
+      <c r="AO4" s="10"/>
+      <c r="AP4" s="11"/>
+      <c r="AQ4" s="10"/>
+      <c r="AR4" s="11"/>
+      <c r="AS4" s="10"/>
+      <c r="AT4" s="8"/>
+      <c r="AU4" s="10"/>
+      <c r="AV4" s="11"/>
+      <c r="AW4" s="10"/>
+      <c r="AX4" s="11"/>
+      <c r="AY4" s="10"/>
+      <c r="AZ4" s="11"/>
+      <c r="BA4" s="10"/>
+      <c r="BB4" s="11"/>
+      <c r="BC4" s="10"/>
+      <c r="BD4" s="11"/>
+      <c r="BE4" s="10"/>
+      <c r="BF4" s="11"/>
+      <c r="BG4" s="10"/>
+      <c r="BH4" s="11"/>
+      <c r="BI4" s="10"/>
+      <c r="BJ4" s="11"/>
+      <c r="BK4" s="10"/>
+      <c r="BL4" s="11"/>
+      <c r="BM4" s="10"/>
+      <c r="BN4" s="11"/>
+      <c r="BO4" s="10"/>
+      <c r="BP4" s="11"/>
+      <c r="BQ4" s="10"/>
+      <c r="BR4" s="11"/>
+      <c r="BS4" s="10"/>
+      <c r="BT4" s="11"/>
+      <c r="BU4" s="10"/>
+      <c r="BV4" s="11"/>
+      <c r="BW4" s="10"/>
+      <c r="BX4" s="11"/>
+      <c r="BY4" s="10"/>
+      <c r="BZ4" s="11"/>
+      <c r="CA4" s="10"/>
+      <c r="CB4" s="11"/>
+      <c r="CC4" s="10"/>
+      <c r="CD4" s="11"/>
+      <c r="CE4" s="10"/>
+      <c r="CF4" s="11"/>
+      <c r="CG4" s="10"/>
     </row>
     <row r="5" ht="36.75" customHeight="1">
-      <c r="A5" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>50</v>
-      </c>
+      <c r="A5" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="23"/>
       <c r="D5" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>50</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="E5" s="10"/>
       <c r="F5" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>54</v>
-      </c>
+      <c r="G5" s="12"/>
       <c r="H5" s="11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="I5" s="12"/>
       <c r="J5" s="8"/>
@@ -1579,24 +1522,22 @@
       <c r="CG5" s="10"/>
     </row>
     <row r="6" ht="36.75" customHeight="1">
-      <c r="A6" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C6" s="31"/>
+      <c r="A6" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="23"/>
       <c r="D6" s="9" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E6" s="10"/>
       <c r="F6" s="11" t="s">
         <v>53</v>
       </c>
       <c r="G6" s="12"/>
-      <c r="H6" s="11" t="s">
-        <v>59</v>
-      </c>
+      <c r="H6" s="11"/>
       <c r="I6" s="12"/>
       <c r="J6" s="8"/>
       <c r="K6" s="10"/>
@@ -1676,21 +1617,23 @@
       <c r="CG6" s="10"/>
     </row>
     <row r="7" ht="36.75" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>60</v>
+      <c r="A7" s="23" t="s">
+        <v>62</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="31"/>
+        <v>63</v>
+      </c>
+      <c r="C7" s="23"/>
       <c r="D7" s="9" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="12"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
       <c r="J7" s="8"/>
@@ -1771,17 +1714,19 @@
       <c r="CG7" s="10"/>
     </row>
     <row r="8" ht="36.75" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>62</v>
+      <c r="A8" s="23" t="s">
+        <v>65</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="31"/>
+        <v>66</v>
+      </c>
+      <c r="C8" s="23"/>
       <c r="D8" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>53</v>
+      </c>
       <c r="F8" s="11" t="s">
         <v>64</v>
       </c>
@@ -1868,21 +1813,21 @@
       <c r="CG8" s="10"/>
     </row>
     <row r="9" ht="36.75" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>65</v>
+      <c r="A9" s="23" t="s">
+        <v>67</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="31"/>
+        <v>68</v>
+      </c>
+      <c r="C9" s="23"/>
       <c r="D9" s="9" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>53</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G9" s="12" t="s">
         <v>53</v>
@@ -1967,15 +1912,15 @@
       <c r="CG9" s="10"/>
     </row>
     <row r="10" ht="36.75" customHeight="1">
-      <c r="A10" s="31" t="s">
-        <v>67</v>
+      <c r="A10" s="23" t="s">
+        <v>69</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="C10" s="31"/>
+        <v>66</v>
+      </c>
+      <c r="C10" s="23"/>
       <c r="D10" s="9" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>53</v>
@@ -1983,9 +1928,7 @@
       <c r="F10" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="G10" s="12" t="s">
-        <v>53</v>
-      </c>
+      <c r="G10" s="12"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
       <c r="J10" s="8"/>
@@ -2066,23 +2009,23 @@
       <c r="CG10" s="10"/>
     </row>
     <row r="11" ht="36.75" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>69</v>
+      <c r="A11" s="23" t="s">
+        <v>71</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C11" s="31"/>
+        <v>72</v>
+      </c>
+      <c r="C11" s="23"/>
       <c r="D11" s="9" t="s">
         <v>70</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="11"/>
+      <c r="G11" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G11" s="12"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
       <c r="J11" s="8"/>
@@ -2163,23 +2106,21 @@
       <c r="CG11" s="10"/>
     </row>
     <row r="12" ht="36.75" customHeight="1">
-      <c r="A12" s="31" t="s">
-        <v>71</v>
+      <c r="A12" s="23" t="s">
+        <v>73</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" s="31"/>
+        <v>74</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>53</v>
+      </c>
       <c r="D12" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>53</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="E12" s="10"/>
       <c r="F12" s="11"/>
-      <c r="G12" s="12" t="s">
-        <v>54</v>
-      </c>
+      <c r="G12" s="12"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
       <c r="J12" s="8"/>
@@ -2260,17 +2201,17 @@
       <c r="CG12" s="10"/>
     </row>
     <row r="13" ht="36.75" customHeight="1">
-      <c r="A13" s="31" t="s">
-        <v>73</v>
+      <c r="A13" s="23" t="s">
+        <v>76</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="23" t="s">
         <v>53</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
@@ -2355,17 +2296,17 @@
       <c r="CG13" s="10"/>
     </row>
     <row r="14" ht="36.75" customHeight="1">
-      <c r="A14" s="31" t="s">
-        <v>76</v>
+      <c r="A14" s="23" t="s">
+        <v>78</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="31" t="s">
-        <v>53</v>
+        <v>79</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>64</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="E14" s="10"/>
       <c r="F14" s="11"/>
@@ -2450,15 +2391,13 @@
       <c r="CG14" s="10"/>
     </row>
     <row r="15" ht="36.75" customHeight="1">
-      <c r="A15" s="31" t="s">
-        <v>78</v>
+      <c r="A15" s="23" t="s">
+        <v>81</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C15" s="31" t="s">
-        <v>64</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="C15" s="23"/>
       <c r="D15" s="9" t="s">
         <v>80</v>
       </c>
@@ -2545,13 +2484,13 @@
       <c r="CG15" s="10"/>
     </row>
     <row r="16" ht="36.75" customHeight="1">
-      <c r="A16" s="31" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" s="31"/>
+      <c r="A16" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="23"/>
       <c r="D16" s="9" t="s">
         <v>80</v>
       </c>
@@ -2638,192 +2577,99 @@
       <c r="CG16" s="10"/>
     </row>
     <row r="17" ht="36.75" customHeight="1">
-      <c r="A17" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="8"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="10"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="10"/>
-      <c r="AB17" s="11"/>
-      <c r="AC17" s="10"/>
-      <c r="AD17" s="11"/>
-      <c r="AE17" s="10"/>
-      <c r="AF17" s="11"/>
-      <c r="AG17" s="10"/>
-      <c r="AH17" s="11"/>
-      <c r="AI17" s="10"/>
-      <c r="AJ17" s="11"/>
-      <c r="AK17" s="10"/>
-      <c r="AL17" s="11"/>
-      <c r="AM17" s="10"/>
-      <c r="AN17" s="11"/>
-      <c r="AO17" s="10"/>
-      <c r="AP17" s="11"/>
-      <c r="AQ17" s="10"/>
-      <c r="AR17" s="11"/>
-      <c r="AS17" s="10"/>
-      <c r="AT17" s="8"/>
-      <c r="AU17" s="10"/>
-      <c r="AV17" s="11"/>
-      <c r="AW17" s="10"/>
-      <c r="AX17" s="11"/>
-      <c r="AY17" s="10"/>
-      <c r="AZ17" s="11"/>
-      <c r="BA17" s="10"/>
-      <c r="BB17" s="11"/>
-      <c r="BC17" s="10"/>
-      <c r="BD17" s="11"/>
-      <c r="BE17" s="10"/>
-      <c r="BF17" s="11"/>
-      <c r="BG17" s="10"/>
-      <c r="BH17" s="11"/>
-      <c r="BI17" s="10"/>
-      <c r="BJ17" s="11"/>
-      <c r="BK17" s="10"/>
-      <c r="BL17" s="11"/>
-      <c r="BM17" s="10"/>
-      <c r="BN17" s="11"/>
-      <c r="BO17" s="10"/>
-      <c r="BP17" s="11"/>
-      <c r="BQ17" s="10"/>
-      <c r="BR17" s="11"/>
-      <c r="BS17" s="10"/>
-      <c r="BT17" s="11"/>
-      <c r="BU17" s="10"/>
-      <c r="BV17" s="11"/>
-      <c r="BW17" s="10"/>
-      <c r="BX17" s="11"/>
-      <c r="BY17" s="10"/>
-      <c r="BZ17" s="11"/>
-      <c r="CA17" s="10"/>
-      <c r="CB17" s="11"/>
-      <c r="CC17" s="10"/>
-      <c r="CD17" s="11"/>
-      <c r="CE17" s="10"/>
-      <c r="CF17" s="11"/>
-      <c r="CG17" s="10"/>
-    </row>
-    <row r="18" ht="36.75" customHeight="1">
-      <c r="A18" s="33" t="s">
+      <c r="A17" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B17" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="35"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="39"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="37"/>
-      <c r="W18" s="34"/>
-      <c r="X18" s="37"/>
-      <c r="Y18" s="34"/>
-      <c r="Z18" s="37"/>
-      <c r="AA18" s="34"/>
-      <c r="AB18" s="37"/>
-      <c r="AC18" s="34"/>
-      <c r="AD18" s="37"/>
-      <c r="AE18" s="34"/>
-      <c r="AF18" s="37"/>
-      <c r="AG18" s="34"/>
-      <c r="AH18" s="37"/>
-      <c r="AI18" s="34"/>
-      <c r="AJ18" s="37"/>
-      <c r="AK18" s="34"/>
-      <c r="AL18" s="37"/>
-      <c r="AM18" s="34"/>
-      <c r="AN18" s="37"/>
-      <c r="AO18" s="34"/>
-      <c r="AP18" s="37"/>
-      <c r="AQ18" s="34"/>
-      <c r="AR18" s="37"/>
-      <c r="AS18" s="34"/>
-      <c r="AT18" s="39"/>
-      <c r="AU18" s="34"/>
-      <c r="AV18" s="37"/>
-      <c r="AW18" s="34"/>
-      <c r="AX18" s="37"/>
-      <c r="AY18" s="34"/>
-      <c r="AZ18" s="37"/>
-      <c r="BA18" s="34"/>
-      <c r="BB18" s="37"/>
-      <c r="BC18" s="34"/>
-      <c r="BD18" s="37"/>
-      <c r="BE18" s="34"/>
-      <c r="BF18" s="37"/>
-      <c r="BG18" s="34"/>
-      <c r="BH18" s="37"/>
-      <c r="BI18" s="34"/>
-      <c r="BJ18" s="37"/>
-      <c r="BK18" s="34"/>
-      <c r="BL18" s="37"/>
-      <c r="BM18" s="34"/>
-      <c r="BN18" s="37"/>
-      <c r="BO18" s="34"/>
-      <c r="BP18" s="37"/>
-      <c r="BQ18" s="34"/>
-      <c r="BR18" s="37"/>
-      <c r="BS18" s="34"/>
-      <c r="BT18" s="37"/>
-      <c r="BU18" s="34"/>
-      <c r="BV18" s="37"/>
-      <c r="BW18" s="34"/>
-      <c r="BX18" s="37"/>
-      <c r="BY18" s="34"/>
-      <c r="BZ18" s="37"/>
-      <c r="CA18" s="34"/>
-      <c r="CB18" s="37"/>
-      <c r="CC18" s="34"/>
-      <c r="CD18" s="37"/>
-      <c r="CE18" s="34"/>
-      <c r="CF18" s="37"/>
-      <c r="CG18" s="34"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="27"/>
+      <c r="N17" s="30"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="30"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="27"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="30"/>
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="27"/>
+      <c r="AD17" s="30"/>
+      <c r="AE17" s="27"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="27"/>
+      <c r="AH17" s="30"/>
+      <c r="AI17" s="27"/>
+      <c r="AJ17" s="30"/>
+      <c r="AK17" s="27"/>
+      <c r="AL17" s="30"/>
+      <c r="AM17" s="27"/>
+      <c r="AN17" s="30"/>
+      <c r="AO17" s="27"/>
+      <c r="AP17" s="30"/>
+      <c r="AQ17" s="27"/>
+      <c r="AR17" s="30"/>
+      <c r="AS17" s="27"/>
+      <c r="AT17" s="32"/>
+      <c r="AU17" s="27"/>
+      <c r="AV17" s="30"/>
+      <c r="AW17" s="27"/>
+      <c r="AX17" s="30"/>
+      <c r="AY17" s="27"/>
+      <c r="AZ17" s="30"/>
+      <c r="BA17" s="27"/>
+      <c r="BB17" s="30"/>
+      <c r="BC17" s="27"/>
+      <c r="BD17" s="30"/>
+      <c r="BE17" s="27"/>
+      <c r="BF17" s="30"/>
+      <c r="BG17" s="27"/>
+      <c r="BH17" s="30"/>
+      <c r="BI17" s="27"/>
+      <c r="BJ17" s="30"/>
+      <c r="BK17" s="27"/>
+      <c r="BL17" s="30"/>
+      <c r="BM17" s="27"/>
+      <c r="BN17" s="30"/>
+      <c r="BO17" s="27"/>
+      <c r="BP17" s="30"/>
+      <c r="BQ17" s="27"/>
+      <c r="BR17" s="30"/>
+      <c r="BS17" s="27"/>
+      <c r="BT17" s="30"/>
+      <c r="BU17" s="27"/>
+      <c r="BV17" s="30"/>
+      <c r="BW17" s="27"/>
+      <c r="BX17" s="30"/>
+      <c r="BY17" s="27"/>
+      <c r="BZ17" s="30"/>
+      <c r="CA17" s="27"/>
+      <c r="CB17" s="30"/>
+      <c r="CC17" s="27"/>
+      <c r="CD17" s="30"/>
+      <c r="CE17" s="27"/>
+      <c r="CF17" s="30"/>
+      <c r="CG17" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
